--- a/artfynd/Bastuberget artfynd.xlsx
+++ b/artfynd/Bastuberget artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56622656</v>
+        <v>260080</v>
       </c>
       <c r="B2" t="n">
-        <v>80112</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bastuberget, Ång</t>
+          <t>Rötjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>683327</v>
+        <v>681754</v>
       </c>
       <c r="R2" t="n">
-        <v>7088067</v>
+        <v>7088140</v>
       </c>
       <c r="S2" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2004-09-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2004-09-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
           <t>Andreas Garpebring</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56622640</v>
+        <v>160053</v>
       </c>
       <c r="B3" t="n">
-        <v>80083</v>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bastuberget, Ång</t>
+          <t>Rötjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>683327</v>
+        <v>681754</v>
       </c>
       <c r="R3" t="n">
-        <v>7088067</v>
+        <v>7088140</v>
       </c>
       <c r="S3" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2004-09-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2004-09-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -853,69 +853,64 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>Andreas Garpebring</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119663607</v>
+        <v>388141</v>
       </c>
       <c r="B4" t="n">
-        <v>92535</v>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Rötjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>682711</v>
+        <v>681754</v>
       </c>
       <c r="R4" t="n">
-        <v>7088886</v>
+        <v>7088140</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -939,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2004-09-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2004-09-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -959,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119663618</v>
+        <v>859839</v>
       </c>
       <c r="B5" t="n">
-        <v>91210</v>
+        <v>96338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Rötjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683216</v>
+        <v>681754</v>
       </c>
       <c r="R5" t="n">
-        <v>7088583</v>
+        <v>7088140</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1036,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2004-09-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2004-09-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1056,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119663492</v>
+        <v>119663501</v>
       </c>
       <c r="B6" t="n">
-        <v>91210</v>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683559</v>
+        <v>682656</v>
       </c>
       <c r="R6" t="n">
-        <v>7088050</v>
+        <v>7088091</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1133,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119663495</v>
+        <v>119663599</v>
       </c>
       <c r="B7" t="n">
-        <v>80118</v>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>683661</v>
+        <v>682673</v>
       </c>
       <c r="R7" t="n">
-        <v>7088104</v>
+        <v>7088638</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1230,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,48 +1257,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56622631</v>
+        <v>119663604</v>
       </c>
       <c r="B8" t="n">
-        <v>57761</v>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bastuberget, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>683106</v>
+        <v>682654</v>
       </c>
       <c r="R8" t="n">
-        <v>7088297</v>
+        <v>7088972</v>
       </c>
       <c r="S8" t="n">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1327,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1347,22 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119663399</v>
+        <v>119663603</v>
       </c>
       <c r="B9" t="n">
-        <v>80083</v>
+        <v>93191</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>683201</v>
+        <v>682656</v>
       </c>
       <c r="R9" t="n">
-        <v>7087667</v>
+        <v>7088961</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1424,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1456,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1566883</v>
+        <v>119663608</v>
       </c>
       <c r="B10" t="n">
-        <v>91263</v>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,37 +1462,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>barrskog, 150 m N om Lill-Bastutjärn, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>683059</v>
+        <v>682675</v>
       </c>
       <c r="R10" t="n">
-        <v>7088526</v>
+        <v>7089003</v>
       </c>
       <c r="S10" t="n">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1521,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2012-08-28</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2012-08-28</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1537,74 +1532,64 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>barrskogsbacke med lövsinslag</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>klen granlåga</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tony Svensson, Staffan Svanberg</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7242871</v>
+        <v>56622665</v>
       </c>
       <c r="B11" t="n">
-        <v>91506</v>
+        <v>79359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bastutjärnen, Ång</t>
+          <t>Bastuberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>683435</v>
+        <v>682978</v>
       </c>
       <c r="R11" t="n">
-        <v>7088306</v>
+        <v>7088088</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1628,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1645,46 +1630,34 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>barrnatur</t>
-        </is>
-      </c>
-      <c r="AN11" t="n">
-        <v>1</v>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>1 substratenheter # tallåga</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Niina Sallmén, Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119663606</v>
+        <v>56622624</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1708,17 +1681,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Bastuberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>682698</v>
+        <v>682978</v>
       </c>
       <c r="R12" t="n">
-        <v>7088906</v>
+        <v>7088088</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1742,12 +1715,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1762,60 +1735,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>56622638</v>
+        <v>119663397</v>
       </c>
       <c r="B13" t="n">
-        <v>80083</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bastuberget, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>683106</v>
+        <v>683215</v>
       </c>
       <c r="R13" t="n">
-        <v>7088297</v>
+        <v>7087675</v>
       </c>
       <c r="S13" t="n">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1839,12 +1812,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1855,31 +1828,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119663490</v>
+        <v>56622639</v>
       </c>
       <c r="B14" t="n">
-        <v>91245</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1887,37 +1855,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Bastuberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>683531</v>
+        <v>682978</v>
       </c>
       <c r="R14" t="n">
-        <v>7088148</v>
+        <v>7088088</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1941,12 +1909,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1957,26 +1925,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119663614</v>
+        <v>119663399</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1984,21 +1957,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2008,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>683120</v>
+        <v>683201</v>
       </c>
       <c r="R15" t="n">
-        <v>7088528</v>
+        <v>7087667</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,12 +2011,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2070,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119663609</v>
+        <v>56622655</v>
       </c>
       <c r="B16" t="n">
-        <v>91210</v>
+        <v>80461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,37 +2054,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Bastuberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>682685</v>
+        <v>682978</v>
       </c>
       <c r="R16" t="n">
-        <v>7088993</v>
+        <v>7088088</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2135,12 +2108,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2155,44 +2128,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119663603</v>
+        <v>119663395</v>
       </c>
       <c r="B17" t="n">
-        <v>92529</v>
+        <v>80461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2202,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>682656</v>
+        <v>683164</v>
       </c>
       <c r="R17" t="n">
-        <v>7088961</v>
+        <v>7087680</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,12 +2205,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2264,10 +2237,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119665743</v>
+        <v>119663398</v>
       </c>
       <c r="B18" t="n">
-        <v>91210</v>
+        <v>80467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2275,21 +2248,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2299,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>682953</v>
+        <v>683201</v>
       </c>
       <c r="R18" t="n">
-        <v>7088445</v>
+        <v>7087667</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,12 +2302,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2361,10 +2334,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119663484</v>
+        <v>56622664</v>
       </c>
       <c r="B19" t="n">
-        <v>80083</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2372,37 +2345,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Bastuberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>683361</v>
+        <v>682978</v>
       </c>
       <c r="R19" t="n">
-        <v>7088466</v>
+        <v>7088088</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2426,12 +2399,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2446,22 +2419,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119663489</v>
+        <v>119663396</v>
       </c>
       <c r="B20" t="n">
-        <v>91210</v>
+        <v>99035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2469,21 +2442,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2493,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>683531</v>
+        <v>683181</v>
       </c>
       <c r="R20" t="n">
-        <v>7088148</v>
+        <v>7087674</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2523,12 +2496,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2555,32 +2528,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119663397</v>
+        <v>119663593</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2590,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>683215</v>
+        <v>683138</v>
       </c>
       <c r="R21" t="n">
-        <v>7087675</v>
+        <v>7088128</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2620,12 +2593,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2652,32 +2625,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119663611</v>
+        <v>119663504</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>106229</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2687,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>682769</v>
+        <v>683124</v>
       </c>
       <c r="R22" t="n">
-        <v>7088948</v>
+        <v>7087715</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2717,12 +2690,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2749,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119663491</v>
+        <v>119663596</v>
       </c>
       <c r="B23" t="n">
-        <v>91263</v>
+        <v>91909</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2760,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2784,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>683583</v>
+        <v>682849</v>
       </c>
       <c r="R23" t="n">
-        <v>7088068</v>
+        <v>7088483</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2814,12 +2787,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2846,10 +2819,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119663497</v>
+        <v>119663615</v>
       </c>
       <c r="B24" t="n">
-        <v>57817</v>
+        <v>91909</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2857,21 +2830,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2881,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>683638</v>
+        <v>682999</v>
       </c>
       <c r="R24" t="n">
-        <v>7088158</v>
+        <v>7088669</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2943,32 +2916,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119663504</v>
+        <v>119663619</v>
       </c>
       <c r="B25" t="n">
-        <v>105381</v>
+        <v>91909</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221725</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2978,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>683124</v>
+        <v>683216</v>
       </c>
       <c r="R25" t="n">
-        <v>7087715</v>
+        <v>7088583</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3008,12 +2981,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3040,48 +3013,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>859839</v>
+        <v>119663598</v>
       </c>
       <c r="B26" t="n">
-        <v>95594</v>
+        <v>93197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2809</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rötjärnliden, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>681754</v>
+        <v>682758</v>
       </c>
       <c r="R26" t="n">
-        <v>7088140</v>
+        <v>7088582</v>
       </c>
       <c r="S26" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3105,12 +3078,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2004-09-06</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2004-09-06</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3125,22 +3098,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>56622625</v>
+        <v>119663607</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>93197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3148,37 +3121,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bastuberget, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>683327</v>
+        <v>682711</v>
       </c>
       <c r="R27" t="n">
-        <v>7088067</v>
+        <v>7088886</v>
       </c>
       <c r="S27" t="n">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3202,12 +3175,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3222,60 +3195,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>56622665</v>
+        <v>119663594</v>
       </c>
       <c r="B28" t="n">
-        <v>79012</v>
+        <v>91872</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bastuberget, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>682978</v>
+        <v>682911</v>
       </c>
       <c r="R28" t="n">
-        <v>7088088</v>
+        <v>7088403</v>
       </c>
       <c r="S28" t="n">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3299,12 +3272,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3315,53 +3288,48 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119663500</v>
+        <v>119663609</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>91872</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3371,10 +3339,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>683638</v>
+        <v>682685</v>
       </c>
       <c r="R29" t="n">
-        <v>7088158</v>
+        <v>7088993</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3401,12 +3369,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3433,10 +3401,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119663395</v>
+        <v>119663618</v>
       </c>
       <c r="B30" t="n">
-        <v>80112</v>
+        <v>91872</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3444,21 +3412,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3468,10 +3436,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>683164</v>
+        <v>683216</v>
       </c>
       <c r="R30" t="n">
-        <v>7087680</v>
+        <v>7088583</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3498,12 +3466,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3530,10 +3498,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119663398</v>
+        <v>119665743</v>
       </c>
       <c r="B31" t="n">
-        <v>80118</v>
+        <v>91872</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3541,21 +3509,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3565,10 +3533,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>683201</v>
+        <v>682953</v>
       </c>
       <c r="R31" t="n">
-        <v>7087667</v>
+        <v>7088445</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3595,12 +3563,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3627,32 +3595,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>56622655</v>
+        <v>56622623</v>
       </c>
       <c r="B32" t="n">
-        <v>80112</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3662,10 +3630,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>682978</v>
+        <v>683106</v>
       </c>
       <c r="R32" t="n">
-        <v>7088088</v>
+        <v>7088297</v>
       </c>
       <c r="S32" t="n">
         <v>250</v>
@@ -3724,32 +3692,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119663598</v>
+        <v>119663590</v>
       </c>
       <c r="B33" t="n">
-        <v>92535</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3759,10 +3727,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>682758</v>
+        <v>682919</v>
       </c>
       <c r="R33" t="n">
-        <v>7088582</v>
+        <v>7088574</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3789,12 +3757,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3821,32 +3789,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119663615</v>
+        <v>119663597</v>
       </c>
       <c r="B34" t="n">
-        <v>91245</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3856,10 +3824,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>682999</v>
+        <v>682843</v>
       </c>
       <c r="R34" t="n">
-        <v>7088669</v>
+        <v>7088496</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3886,12 +3854,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3918,14 +3886,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119663590</v>
+        <v>119663606</v>
       </c>
       <c r="B35" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -3953,10 +3921,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>682919</v>
+        <v>682698</v>
       </c>
       <c r="R35" t="n">
-        <v>7088574</v>
+        <v>7088906</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3983,12 +3951,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4015,48 +3983,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>56622629</v>
+        <v>119663611</v>
       </c>
       <c r="B36" t="n">
-        <v>91263</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bastuberget, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>683106</v>
+        <v>682769</v>
       </c>
       <c r="R36" t="n">
-        <v>7088297</v>
+        <v>7088948</v>
       </c>
       <c r="S36" t="n">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4080,12 +4048,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4096,53 +4064,48 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119663596</v>
+        <v>119663614</v>
       </c>
       <c r="B37" t="n">
-        <v>91245</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4152,10 +4115,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>682849</v>
+        <v>683120</v>
       </c>
       <c r="R37" t="n">
-        <v>7088483</v>
+        <v>7088528</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4182,12 +4145,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4214,32 +4177,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119663619</v>
+        <v>119663617</v>
       </c>
       <c r="B38" t="n">
-        <v>91245</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4249,10 +4212,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>683216</v>
+        <v>683033</v>
       </c>
       <c r="R38" t="n">
-        <v>7088583</v>
+        <v>7088610</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4311,10 +4274,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119663612</v>
+        <v>119663602</v>
       </c>
       <c r="B39" t="n">
-        <v>91245</v>
+        <v>79084</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4322,21 +4285,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4346,10 +4309,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>683357</v>
+        <v>682680</v>
       </c>
       <c r="R39" t="n">
-        <v>7088112</v>
+        <v>7088918</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4376,12 +4339,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4408,44 +4371,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>5989014</v>
+        <v>56622638</v>
       </c>
       <c r="B40" t="n">
-        <v>98281</v>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>223597</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>kärr, 250 m NNO om Lill-Basutjärn, Ång</t>
+          <t>Bastuberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>683118</v>
+        <v>683106</v>
       </c>
       <c r="R40" t="n">
-        <v>7088607</v>
+        <v>7088297</v>
       </c>
       <c r="S40" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4469,12 +4436,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2012-08-28</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2012-08-28</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4486,65 +4453,65 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>trädbevuxet kärr</t>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Tony Svensson, Staffan Svanberg</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>56622639</v>
+        <v>2071852</v>
       </c>
       <c r="B41" t="n">
-        <v>80083</v>
+        <v>80461</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bastuberget, Ång</t>
+          <t>barrskog, 150 m N om Lill-Bastutjärn, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>682978</v>
+        <v>683059</v>
       </c>
       <c r="R41" t="n">
-        <v>7088088</v>
+        <v>7088526</v>
       </c>
       <c r="S41" t="n">
         <v>250</v>
@@ -4571,12 +4538,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2012-08-28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2012-08-28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4588,68 +4555,73 @@
       <c r="AG41" t="b">
         <v>0</v>
       </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>barrskogsbacke med lövsinslag</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Tony Svensson, Staffan Svanberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119665744</v>
+        <v>56622654</v>
       </c>
       <c r="B42" t="n">
-        <v>91263</v>
+        <v>80461</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Bastuberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>682838</v>
+        <v>683106</v>
       </c>
       <c r="R42" t="n">
-        <v>7088521</v>
+        <v>7088297</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4673,12 +4645,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4693,22 +4665,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119663496</v>
+        <v>119663595</v>
       </c>
       <c r="B43" t="n">
-        <v>98265</v>
+        <v>80461</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4716,21 +4688,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220093</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4740,10 +4712,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>683640</v>
+        <v>682866</v>
       </c>
       <c r="R43" t="n">
-        <v>7088118</v>
+        <v>7088413</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4770,12 +4742,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4802,10 +4774,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119663485</v>
+        <v>119663616</v>
       </c>
       <c r="B44" t="n">
-        <v>79987</v>
+        <v>80461</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4813,21 +4785,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4837,10 +4809,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>683361</v>
+        <v>683021</v>
       </c>
       <c r="R44" t="n">
-        <v>7088466</v>
+        <v>7088652</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4899,48 +4871,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>260080</v>
+        <v>119665740</v>
       </c>
       <c r="B45" t="n">
-        <v>79012</v>
+        <v>80461</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Rötjärnliden, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>681754</v>
+        <v>682951</v>
       </c>
       <c r="R45" t="n">
-        <v>7088140</v>
+        <v>7088538</v>
       </c>
       <c r="S45" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4964,12 +4936,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2004-09-06</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2004-09-06</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4984,22 +4956,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119663486</v>
+        <v>119663610</v>
       </c>
       <c r="B46" t="n">
-        <v>80112</v>
+        <v>57144</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5007,21 +4979,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>102613</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5031,10 +5003,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>683361</v>
+        <v>682754</v>
       </c>
       <c r="R46" t="n">
-        <v>7088466</v>
+        <v>7088971</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5061,12 +5033,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5093,48 +5065,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119663595</v>
+        <v>56622631</v>
       </c>
       <c r="B47" t="n">
-        <v>80112</v>
+        <v>58057</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>103031</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Bastuberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>682866</v>
+        <v>683106</v>
       </c>
       <c r="R47" t="n">
-        <v>7088413</v>
+        <v>7088297</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5158,12 +5130,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5178,60 +5150,56 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119663617</v>
+        <v>5989014</v>
       </c>
       <c r="B48" t="n">
-        <v>78980</v>
+        <v>99038</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>223597</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>kärr, 250 m NNO om Lill-Basutjärn, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>683033</v>
+        <v>683118</v>
       </c>
       <c r="R48" t="n">
-        <v>7088610</v>
+        <v>7088607</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5255,12 +5223,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2012-08-28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2012-08-28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5271,48 +5239,53 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>trädbevuxet kärr</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Tony Svensson, Staffan Svanberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119663616</v>
+        <v>119663605</v>
       </c>
       <c r="B49" t="n">
-        <v>80112</v>
+        <v>79085</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5322,10 +5295,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>683021</v>
+        <v>682702</v>
       </c>
       <c r="R49" t="n">
-        <v>7088652</v>
+        <v>7088927</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5352,12 +5325,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5384,10 +5357,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119663604</v>
+        <v>119663490</v>
       </c>
       <c r="B50" t="n">
-        <v>92527</v>
+        <v>91909</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5395,21 +5368,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5419,10 +5392,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>682654</v>
+        <v>683531</v>
       </c>
       <c r="R50" t="n">
-        <v>7088972</v>
+        <v>7088148</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5449,12 +5422,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5481,32 +5454,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119663610</v>
+        <v>119663612</v>
       </c>
       <c r="B51" t="n">
-        <v>56852</v>
+        <v>91909</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102613</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5516,10 +5489,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>682754</v>
+        <v>683357</v>
       </c>
       <c r="R51" t="n">
-        <v>7088971</v>
+        <v>7088112</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5546,12 +5519,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5578,10 +5551,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119665740</v>
+        <v>119663489</v>
       </c>
       <c r="B52" t="n">
-        <v>80112</v>
+        <v>91872</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5589,21 +5562,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5613,10 +5586,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>682951</v>
+        <v>683531</v>
       </c>
       <c r="R52" t="n">
-        <v>7088538</v>
+        <v>7088148</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5643,12 +5616,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5675,32 +5648,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119663597</v>
+        <v>119663492</v>
       </c>
       <c r="B53" t="n">
-        <v>78980</v>
+        <v>91872</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5710,10 +5683,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>682843</v>
+        <v>683559</v>
       </c>
       <c r="R53" t="n">
-        <v>7088496</v>
+        <v>7088050</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5740,12 +5713,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5772,14 +5745,14 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119663487</v>
+        <v>56622625</v>
       </c>
       <c r="B54" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -5803,17 +5776,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Bastuberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>683510</v>
+        <v>683327</v>
       </c>
       <c r="R54" t="n">
-        <v>7088124</v>
+        <v>7088067</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5837,12 +5810,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5857,44 +5830,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119663502</v>
+        <v>119663487</v>
       </c>
       <c r="B55" t="n">
-        <v>91263</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5904,10 +5877,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>683107</v>
+        <v>683510</v>
       </c>
       <c r="R55" t="n">
-        <v>7087724</v>
+        <v>7088124</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5934,12 +5907,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5966,32 +5939,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119663594</v>
+        <v>119663500</v>
       </c>
       <c r="B56" t="n">
-        <v>91210</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6001,10 +5974,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>682911</v>
+        <v>683638</v>
       </c>
       <c r="R56" t="n">
-        <v>7088403</v>
+        <v>7088158</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6031,12 +6004,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6063,48 +6036,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119663605</v>
+        <v>56622648</v>
       </c>
       <c r="B57" t="n">
-        <v>78739</v>
+        <v>80336</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Bastuberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>682702</v>
+        <v>683327</v>
       </c>
       <c r="R57" t="n">
-        <v>7088927</v>
+        <v>7088067</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6128,12 +6101,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6144,26 +6117,31 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119663592</v>
+        <v>119663494</v>
       </c>
       <c r="B58" t="n">
-        <v>56852</v>
+        <v>80336</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6171,21 +6149,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>102613</v>
+        <v>6456</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6195,10 +6173,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>683395</v>
+        <v>683661</v>
       </c>
       <c r="R58" t="n">
-        <v>7087897</v>
+        <v>7088104</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6225,12 +6203,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6257,10 +6235,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119663599</v>
+        <v>56622640</v>
       </c>
       <c r="B59" t="n">
-        <v>78647</v>
+        <v>80432</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6268,37 +6246,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Bastuberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>682673</v>
+        <v>683327</v>
       </c>
       <c r="R59" t="n">
-        <v>7088638</v>
+        <v>7088067</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6322,12 +6300,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6338,64 +6316,69 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119663602</v>
+        <v>56622656</v>
       </c>
       <c r="B60" t="n">
-        <v>78738</v>
+        <v>80461</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Bastuberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>682680</v>
+        <v>683327</v>
       </c>
       <c r="R60" t="n">
-        <v>7088918</v>
+        <v>7088067</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6419,12 +6402,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2014-08-28</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6439,39 +6422,39 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>56622623</v>
+        <v>119663495</v>
       </c>
       <c r="B61" t="n">
-        <v>78980</v>
+        <v>80467</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6482,17 +6465,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bastuberget, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>683106</v>
+        <v>683661</v>
       </c>
       <c r="R61" t="n">
-        <v>7088297</v>
+        <v>7088104</v>
       </c>
       <c r="S61" t="n">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6516,12 +6499,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6536,60 +6519,60 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>56622624</v>
+        <v>119663592</v>
       </c>
       <c r="B62" t="n">
-        <v>78980</v>
+        <v>57144</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bastuberget, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>682978</v>
+        <v>683395</v>
       </c>
       <c r="R62" t="n">
-        <v>7088088</v>
+        <v>7087897</v>
       </c>
       <c r="S62" t="n">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6613,12 +6596,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6633,60 +6616,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>56622654</v>
+        <v>119663497</v>
       </c>
       <c r="B63" t="n">
-        <v>80112</v>
+        <v>58114</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Bastuberget, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>683106</v>
+        <v>683638</v>
       </c>
       <c r="R63" t="n">
-        <v>7088297</v>
+        <v>7088158</v>
       </c>
       <c r="S63" t="n">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6710,12 +6693,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6730,22 +6713,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119663396</v>
+        <v>119663496</v>
       </c>
       <c r="B64" t="n">
-        <v>98278</v>
+        <v>99022</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6753,21 +6736,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219790</v>
+        <v>220093</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6777,10 +6760,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>683181</v>
+        <v>683640</v>
       </c>
       <c r="R64" t="n">
-        <v>7087674</v>
+        <v>7088118</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6807,12 +6790,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6839,48 +6822,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119663488</v>
+        <v>7242871</v>
       </c>
       <c r="B65" t="n">
-        <v>91263</v>
+        <v>92183</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>65</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Bastutjärnen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>683532</v>
+        <v>683435</v>
       </c>
       <c r="R65" t="n">
-        <v>7088084</v>
+        <v>7088306</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6904,12 +6887,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6920,26 +6903,43 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>barrnatur</t>
+        </is>
+      </c>
+      <c r="AN65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>1 substratenheter # tallåga</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
+          <t>Ulrika Westling, Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2071852</v>
+        <v>119663485</v>
       </c>
       <c r="B66" t="n">
-        <v>80112</v>
+        <v>80336</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6947,37 +6947,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>barrskog, 150 m N om Lill-Bastutjärn, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>683059</v>
+        <v>683361</v>
       </c>
       <c r="R66" t="n">
-        <v>7088526</v>
+        <v>7088466</v>
       </c>
       <c r="S66" t="n">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7001,12 +7001,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2012-08-28</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2012-08-28</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7017,36 +7017,26 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>barrskogsbacke med lövsinslag</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Tony Svensson, Staffan Svanberg</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>160053</v>
+        <v>119663484</v>
       </c>
       <c r="B67" t="n">
-        <v>88654</v>
+        <v>80432</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7054,37 +7044,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Rötjärnliden, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>681754</v>
+        <v>683361</v>
       </c>
       <c r="R67" t="n">
-        <v>7088140</v>
+        <v>7088466</v>
       </c>
       <c r="S67" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7108,12 +7098,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2004-09-06</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2004-09-06</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7128,60 +7118,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>56622664</v>
+        <v>119663486</v>
       </c>
       <c r="B68" t="n">
-        <v>57657</v>
+        <v>80461</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Bastuberget, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>682978</v>
+        <v>683361</v>
       </c>
       <c r="R68" t="n">
-        <v>7088088</v>
+        <v>7088466</v>
       </c>
       <c r="S68" t="n">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7205,12 +7195,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2014-08-28</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7225,602 +7215,15 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>388141</v>
-      </c>
-      <c r="B69" t="n">
-        <v>82792</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Rötjärnliden, Ång</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>681754</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7088140</v>
-      </c>
-      <c r="S69" t="n">
-        <v>100</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2004-09-06</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2004-09-06</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Jonas F Grahn</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Andreas Garpebring</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>56622648</v>
-      </c>
-      <c r="B70" t="n">
-        <v>79987</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>6456</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Skinnlav</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Bastuberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>683327</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7088067</v>
-      </c>
-      <c r="S70" t="n">
-        <v>250</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2014-08-28</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2014-08-28</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Andreas Garpebring</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Torbjörn Josefsson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>119663501</v>
-      </c>
-      <c r="B71" t="n">
-        <v>91210</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Bjurholm, Ång</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>682656</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7088091</v>
-      </c>
-      <c r="S71" t="n">
-        <v>10</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Hanna Bäckman</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Hanna Bäckman</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>119663613</v>
-      </c>
-      <c r="B72" t="n">
-        <v>91263</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Bjurholm, Ång</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>683344</v>
-      </c>
-      <c r="R72" t="n">
-        <v>7088284</v>
-      </c>
-      <c r="S72" t="n">
-        <v>10</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Hanna Bäckman</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>Hanna Bäckman</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>119663494</v>
-      </c>
-      <c r="B73" t="n">
-        <v>79987</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>6456</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Skinnlav</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Leptogium saturninum</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Bjurholm, Ång</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>683661</v>
-      </c>
-      <c r="R73" t="n">
-        <v>7088104</v>
-      </c>
-      <c r="S73" t="n">
-        <v>10</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Hanna Bäckman</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Hanna Bäckman</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>119663593</v>
-      </c>
-      <c r="B74" t="n">
-        <v>98361</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Bjurholm, Ång</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>683138</v>
-      </c>
-      <c r="R74" t="n">
-        <v>7088128</v>
-      </c>
-      <c r="S74" t="n">
-        <v>10</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2024-08-14</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2024-08-14</t>
-        </is>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Hanna Bäckman</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>Hanna Bäckman</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
